--- a/code.xlsx
+++ b/code.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VIGNESH V\OneDrive\Desktop\python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{00B44E7D-0D69-4165-A760-A18A184A0263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B32774B-F5EB-42FD-BCFE-5E97CD52F1DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E0014342-BFD7-400F-A66B-88C734AB7B7A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{E0014342-BFD7-400F-A66B-88C734AB7B7A}"/>
   </bookViews>
   <sheets>
     <sheet name="String" sheetId="1" r:id="rId1"/>
+    <sheet name="Git" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -27,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
   <si>
     <t>Java</t>
   </si>
@@ -184,6 +183,52 @@
   </si>
   <si>
     <t>Na</t>
+  </si>
+  <si>
+    <t>To Check the git is insatalled properly</t>
+  </si>
+  <si>
+    <t>to login</t>
+  </si>
+  <si>
+    <t>git --version</t>
+  </si>
+  <si>
+    <t>git config --global user.name "vigneshvrthn"</t>
+  </si>
+  <si>
+    <t>git config --global user.email "vigneshvrthn@gmail.com"</t>
+  </si>
+  <si>
+    <t>git init</t>
+  </si>
+  <si>
+    <t>to initialization</t>
+  </si>
+  <si>
+    <t>git add .</t>
+  </si>
+  <si>
+    <t>to add files</t>
+  </si>
+  <si>
+    <t>git commit -m "save"</t>
+  </si>
+  <si>
+    <t>make the commitment</t>
+  </si>
+  <si>
+    <t>git remote add origin https://github.com/vigneshvrthn/study.git</t>
+  </si>
+  <si>
+    <t>conntect with repo</t>
+  </si>
+  <si>
+    <t>git branch -M main
+git push -u origin main</t>
+  </si>
+  <si>
+    <t xml:space="preserve">for first push </t>
   </si>
 </sst>
 </file>
@@ -241,7 +286,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -250,6 +295,14 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -763,4 +816,83 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2539D1C-5624-4924-A62D-8446AC560FE6}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="53.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="6"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:B3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/code.xlsx
+++ b/code.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VIGNESH V\OneDrive\Desktop\python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B32774B-F5EB-42FD-BCFE-5E97CD52F1DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{075A2D67-2482-46D5-977A-D88557AE8815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{E0014342-BFD7-400F-A66B-88C734AB7B7A}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="72">
   <si>
     <t>Java</t>
   </si>
@@ -229,6 +229,30 @@
   </si>
   <si>
     <t xml:space="preserve">for first push </t>
+  </si>
+  <si>
+    <t xml:space="preserve">after first time push we can use to upadet the files when we make any changes </t>
+  </si>
+  <si>
+    <t>git push</t>
+  </si>
+  <si>
+    <t>git clone https://github.com/vignesh/flutter_project.git</t>
+  </si>
+  <si>
+    <t>if need to download the file  use this if the project is not in the pc</t>
+  </si>
+  <si>
+    <t>git pull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to get the latest file in git </t>
+  </si>
+  <si>
+    <t xml:space="preserve">git remove -v </t>
+  </si>
+  <si>
+    <t>to check the current git repo</t>
   </si>
 </sst>
 </file>
@@ -286,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -298,10 +322,19 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -820,7 +853,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2539D1C-5624-4924-A62D-8446AC560FE6}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="53.44140625" bestFit="1" customWidth="1"/>
@@ -839,7 +872,7 @@
       <c r="A2" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>50</v>
       </c>
     </row>
@@ -847,10 +880,10 @@
       <c r="A3" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="6"/>
+      <c r="B3" s="7"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="5" t="s">
         <v>54</v>
       </c>
       <c r="B4" s="5" t="s">
@@ -858,7 +891,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="5" t="s">
         <v>56</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -866,7 +899,7 @@
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="5" t="s">
         <v>58</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -874,7 +907,7 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="5" t="s">
         <v>60</v>
       </c>
       <c r="B7" s="5" t="s">
@@ -882,16 +915,61 @@
       </c>
     </row>
     <row r="8" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>63</v>
       </c>
     </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="9"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="9"/>
+    </row>
+    <row r="12" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B9:B11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/code.xlsx
+++ b/code.xlsx
@@ -310,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -325,17 +325,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -872,7 +868,7 @@
       <c r="A2" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>50</v>
       </c>
     </row>
@@ -880,7 +876,7 @@
       <c r="A3" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="7"/>
+      <c r="B3" s="8"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
@@ -923,7 +919,7 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="5" t="s">
         <v>56</v>
       </c>
       <c r="B9" s="9" t="s">
@@ -931,38 +927,38 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="5" t="s">
         <v>58</v>
       </c>
       <c r="B10" s="9"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="5" t="s">
         <v>65</v>
       </c>
       <c r="B11" s="9"/>
     </row>
     <row r="12" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="6" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="5" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="5" t="s">
         <v>71</v>
       </c>
     </row>
